--- a/db/library/library-books.xlsx
+++ b/db/library/library-books.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\manapristine\db\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA53BC9-7822-4E80-8717-D875A3C8C893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A3B13A-0089-4107-9003-0A05D9AFE538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="477">
   <si>
     <t>Sr#</t>
   </si>
@@ -1446,6 +1446,12 @@
   </si>
   <si>
     <t>Know your child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Geographic </t>
+  </si>
+  <si>
+    <t>National Geographic</t>
   </si>
 </sst>
 </file>
@@ -1870,8 +1876,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:H240" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A1:H240" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:H241" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A1:H241" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sr#" dataDxfId="7"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Book Name" dataDxfId="6"/>
@@ -2183,7 +2189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H240"/>
+  <dimension ref="A1:H241"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.6640625" style="12" customWidth="1"/>
@@ -8433,6 +8439,32 @@
         <v>12</v>
       </c>
       <c r="H240" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A241" s="15">
+        <v>239</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="C241" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="D241" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E241" s="18">
+        <v>21</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G241" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H241" s="13" t="s">
         <v>13</v>
       </c>
     </row>
